--- a/EXECUÇÃO 2319 2026.xlsx
+++ b/EXECUÇÃO 2319 2026.xlsx
@@ -540,11 +540,11 @@
         <v>690009410</v>
       </c>
       <c r="D23" s="12">
-        <v>71102330.5</v>
+        <v>71100080.5</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="13">
-        <v>618907079.5</v>
+        <v>618909329.5</v>
       </c>
     </row>
     <row r="24">
@@ -848,13 +848,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C2300DD-E3A8-4FFC-8D78-6ED57C737D81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23FA6776-82D0-4E8B-843B-6FC9D62202BE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDE19F39-B5C4-4FA3-BFD9-E08B9CD5183C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8334880E-AC1E-45D6-B2B6-068D14B9A401}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C69C636F-738A-4CA0-8D21-099C1BD47559}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC4B3C62-CA75-4A85-8528-EED28D530320}"/>
 </file>
--- a/EXECUÇÃO 2319 2026.xlsx
+++ b/EXECUÇÃO 2319 2026.xlsx
@@ -481,9 +481,11 @@
       <c r="C20" s="12">
         <v>64382751</v>
       </c>
-      <c r="D20" s="12"/>
+      <c r="D20" s="12">
+        <v>765549</v>
+      </c>
       <c r="E20" s="12">
-        <v>2015553</v>
+        <v>1250004</v>
       </c>
       <c r="F20" s="13">
         <v>62367198</v>
@@ -520,13 +522,13 @@
         <v>1250000000</v>
       </c>
       <c r="D22" s="12">
-        <v>106371312.34</v>
+        <v>95225046.67</v>
       </c>
       <c r="E22" s="12">
         <v>234401069</v>
       </c>
       <c r="F22" s="13">
-        <v>909227618.66</v>
+        <v>920373884.33</v>
       </c>
     </row>
     <row r="23">
@@ -540,11 +542,11 @@
         <v>690009410</v>
       </c>
       <c r="D23" s="12">
-        <v>71100080.5</v>
+        <v>27567340.5</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="13">
-        <v>618909329.5</v>
+        <v>662442069.5</v>
       </c>
     </row>
     <row r="24">
@@ -848,13 +850,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23FA6776-82D0-4E8B-843B-6FC9D62202BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF1B8F93-E14E-4553-98AD-51A265CDE803}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8334880E-AC1E-45D6-B2B6-068D14B9A401}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF20E22F-EF75-42DA-972F-C87F5B08E821}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC4B3C62-CA75-4A85-8528-EED28D530320}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7613F945-80AF-48CD-AAB9-85A91B9748BC}"/>
 </file>